--- a/artfynd/A 18712-2026 artfynd.xlsx
+++ b/artfynd/A 18712-2026 artfynd.xlsx
@@ -1417,42 +1417,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133406923</v>
+        <v>133406888</v>
       </c>
       <c r="B9" t="n">
-        <v>57955</v>
+        <v>106258</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1460,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601731</v>
+        <v>601715</v>
       </c>
       <c r="R9" t="n">
-        <v>6425397</v>
+        <v>6425424</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1498,17 +1502,13 @@
           <t>2026-05-13</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Spår av födosk</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1527,46 +1527,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133406888</v>
+        <v>133406923</v>
       </c>
       <c r="B10" t="n">
-        <v>106258</v>
+        <v>57955</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1574,10 +1570,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>601715</v>
+        <v>601731</v>
       </c>
       <c r="R10" t="n">
-        <v>6425424</v>
+        <v>6425397</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1612,13 +1608,17 @@
           <t>2026-05-13</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Spår av födosk</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 18712-2026 artfynd.xlsx
+++ b/artfynd/A 18712-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133407134</v>
+        <v>133406923</v>
       </c>
       <c r="B2" t="n">
-        <v>99178</v>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601701</v>
+        <v>601731</v>
       </c>
       <c r="R2" t="n">
-        <v>6425436</v>
+        <v>6425397</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,13 +756,17 @@
           <t>2026-05-13</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Spår av födosk</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,42 +785,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133407115</v>
+        <v>133407004</v>
       </c>
       <c r="B3" t="n">
-        <v>99178</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601705</v>
+        <v>601724</v>
       </c>
       <c r="R3" t="n">
-        <v>6425430</v>
+        <v>6425393</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,13 +866,17 @@
           <t>2026-05-13</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Spår av födosök, barkborregran</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,56 +895,60 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133406949</v>
+        <v>133407187</v>
       </c>
       <c r="B4" t="n">
-        <v>99178</v>
+        <v>57391</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>102961</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 18712, Averum, Sm</t>
+          <t>Ärmdalen, Averum, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601725</v>
+        <v>601675</v>
       </c>
       <c r="R4" t="n">
-        <v>6425401</v>
+        <v>6425492</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +986,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -993,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133406629</v>
+        <v>133406564</v>
       </c>
       <c r="B5" t="n">
-        <v>99178</v>
+        <v>99195</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601612</v>
+        <v>601626</v>
       </c>
       <c r="R5" t="n">
-        <v>6425456</v>
+        <v>6425448</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133407124</v>
+        <v>133406577</v>
       </c>
       <c r="B6" t="n">
-        <v>99178</v>
+        <v>99195</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1142,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601706</v>
+        <v>601612</v>
       </c>
       <c r="R6" t="n">
-        <v>6425431</v>
+        <v>6425452</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1216,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133407070</v>
+        <v>133406629</v>
       </c>
       <c r="B7" t="n">
-        <v>99178</v>
+        <v>99195</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1248,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601717</v>
+        <v>601612</v>
       </c>
       <c r="R7" t="n">
-        <v>6425423</v>
+        <v>6425456</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133406668</v>
+        <v>133406647</v>
       </c>
       <c r="B8" t="n">
-        <v>99178</v>
+        <v>99195</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,10 +1365,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601620</v>
+        <v>601609</v>
       </c>
       <c r="R8" t="n">
-        <v>6425452</v>
+        <v>6425439</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,42 +1428,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133406923</v>
+        <v>133406668</v>
       </c>
       <c r="B9" t="n">
-        <v>57972</v>
+        <v>99195</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1460,10 +1471,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601731</v>
+        <v>601620</v>
       </c>
       <c r="R9" t="n">
-        <v>6425397</v>
+        <v>6425452</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1498,17 +1509,13 @@
           <t>2026-05-13</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Spår av födosk</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1527,32 +1534,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133406888</v>
+        <v>133406690</v>
       </c>
       <c r="B10" t="n">
-        <v>106307</v>
+        <v>99195</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,11 +1568,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1574,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>601715</v>
+        <v>601602</v>
       </c>
       <c r="R10" t="n">
-        <v>6425424</v>
+        <v>6425445</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1637,10 +1640,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133407091</v>
+        <v>133406722</v>
       </c>
       <c r="B11" t="n">
-        <v>99178</v>
+        <v>99195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601705</v>
+        <v>601620</v>
       </c>
       <c r="R11" t="n">
-        <v>6425428</v>
+        <v>6425405</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,32 +1746,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133406867</v>
+        <v>133406767</v>
       </c>
       <c r="B12" t="n">
-        <v>106307</v>
+        <v>99195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1786,10 +1789,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601704</v>
+        <v>601608</v>
       </c>
       <c r="R12" t="n">
-        <v>6425409</v>
+        <v>6425391</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1849,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133406577</v>
+        <v>133406803</v>
       </c>
       <c r="B13" t="n">
-        <v>99178</v>
+        <v>99195</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,10 +1895,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601612</v>
+        <v>601632</v>
       </c>
       <c r="R13" t="n">
-        <v>6425452</v>
+        <v>6425398</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1955,10 +1958,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133406803</v>
+        <v>133406949</v>
       </c>
       <c r="B14" t="n">
-        <v>99178</v>
+        <v>99195</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1998,10 +2001,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601632</v>
+        <v>601725</v>
       </c>
       <c r="R14" t="n">
-        <v>6425398</v>
+        <v>6425401</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2061,42 +2064,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133407004</v>
+        <v>133407022</v>
       </c>
       <c r="B15" t="n">
-        <v>57972</v>
+        <v>99195</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2104,10 +2107,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>601724</v>
+        <v>601730</v>
       </c>
       <c r="R15" t="n">
-        <v>6425393</v>
+        <v>6425426</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2142,17 +2145,13 @@
           <t>2026-05-13</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Spår av födosök, barkborregran</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2171,10 +2170,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133406564</v>
+        <v>133407040</v>
       </c>
       <c r="B16" t="n">
-        <v>99178</v>
+        <v>99195</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2214,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>601626</v>
+        <v>601725</v>
       </c>
       <c r="R16" t="n">
-        <v>6425448</v>
+        <v>6425421</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2277,32 +2276,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133406835</v>
+        <v>133407056</v>
       </c>
       <c r="B17" t="n">
-        <v>106307</v>
+        <v>99195</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2311,11 +2310,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -2324,10 +2319,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>601707</v>
+        <v>601725</v>
       </c>
       <c r="R17" t="n">
-        <v>6425406</v>
+        <v>6425420</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2387,10 +2382,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133407040</v>
+        <v>133407070</v>
       </c>
       <c r="B18" t="n">
-        <v>99178</v>
+        <v>99195</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2430,10 +2425,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>601725</v>
+        <v>601717</v>
       </c>
       <c r="R18" t="n">
-        <v>6425421</v>
+        <v>6425423</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2493,10 +2488,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133407056</v>
+        <v>133407091</v>
       </c>
       <c r="B19" t="n">
-        <v>99178</v>
+        <v>99195</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2536,10 +2531,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>601725</v>
+        <v>601705</v>
       </c>
       <c r="R19" t="n">
-        <v>6425420</v>
+        <v>6425428</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2596,6 +2591,650 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>133407115</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>A 18712, Averum, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>601705</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6425430</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Loftahammar</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>133407124</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>A 18712, Averum, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>601706</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6425431</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Loftahammar</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>133407134</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>A 18712, Averum, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>601701</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6425436</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Loftahammar</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>133406835</v>
+      </c>
+      <c r="B23" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>A 18712, Averum, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>601707</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6425406</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Loftahammar</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>133406867</v>
+      </c>
+      <c r="B24" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>A 18712, Averum, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>601704</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6425409</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Loftahammar</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>133406888</v>
+      </c>
+      <c r="B25" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>A 18712, Averum, Sm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>601715</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6425424</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Loftahammar</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
